--- a/20250519_SA_ternary/output/system_analysis/system_analysis_files.xlsx
+++ b/20250519_SA_ternary/output/system_analysis/system_analysis_files.xlsx
@@ -40,25 +40,46 @@
     <t>Er-In</t>
   </si>
   <si>
+    <t>1956508</t>
+  </si>
+  <si>
+    <t>1000761</t>
+  </si>
+  <si>
+    <t>1803318</t>
+  </si>
+  <si>
+    <t>1814810</t>
+  </si>
+  <si>
+    <t>1634753</t>
+  </si>
+  <si>
+    <t>1710931</t>
+  </si>
+  <si>
+    <t>1840445</t>
+  </si>
+  <si>
+    <t>1229705</t>
+  </si>
+  <si>
+    <t>1234749</t>
+  </si>
+  <si>
+    <t>1920543</t>
+  </si>
+  <si>
     <t>1818414</t>
   </si>
   <si>
-    <t>1956508</t>
-  </si>
-  <si>
-    <t>1000761</t>
-  </si>
-  <si>
-    <t>1814810</t>
-  </si>
-  <si>
-    <t>1234749</t>
-  </si>
-  <si>
-    <t>1634753</t>
-  </si>
-  <si>
-    <t>1710931</t>
+    <t>1233938</t>
+  </si>
+  <si>
+    <t>1803512</t>
+  </si>
+  <si>
+    <t>1925389</t>
   </si>
   <si>
     <t>1140826</t>
@@ -67,58 +88,37 @@
     <t>1234747</t>
   </si>
   <si>
-    <t>1840445</t>
-  </si>
-  <si>
-    <t>1229705</t>
-  </si>
-  <si>
-    <t>1920543</t>
-  </si>
-  <si>
-    <t>1925389</t>
-  </si>
-  <si>
-    <t>1233938</t>
-  </si>
-  <si>
-    <t>1803512</t>
-  </si>
-  <si>
-    <t>1803318</t>
+    <t>Lu3Co2In4</t>
+  </si>
+  <si>
+    <t>Lu14Co2In3</t>
+  </si>
+  <si>
+    <t>Gd14Co3In2.7</t>
+  </si>
+  <si>
+    <t>HoCoGa5</t>
+  </si>
+  <si>
+    <t>Nd11Pd4In9</t>
+  </si>
+  <si>
+    <t>PuNi3</t>
+  </si>
+  <si>
+    <t>Ho2CoGa8</t>
   </si>
   <si>
     <t>Ho6Co2Ga</t>
   </si>
   <si>
-    <t>Lu3Co2In4</t>
-  </si>
-  <si>
-    <t>Gd14Co3In2.7</t>
-  </si>
-  <si>
-    <t>PuNi3</t>
-  </si>
-  <si>
-    <t>HoCoGa5</t>
+    <t>Ho10Ni9In20</t>
+  </si>
+  <si>
+    <t>MgCu4Sn</t>
   </si>
   <si>
     <t>Pr8CoGa3</t>
-  </si>
-  <si>
-    <t>Nd11Pd4In9</t>
-  </si>
-  <si>
-    <t>Ho2CoGa8</t>
-  </si>
-  <si>
-    <t>MgCu4Sn</t>
-  </si>
-  <si>
-    <t>Ho10Ni9In20</t>
-  </si>
-  <si>
-    <t>Lu14Co2In3</t>
   </si>
   <si>
     <t>All files</t>
@@ -525,19 +525,19 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -545,7 +545,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -629,19 +629,19 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -649,7 +649,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -681,19 +681,19 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -701,7 +701,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -713,10 +713,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -733,16 +733,16 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -759,19 +759,19 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -779,22 +779,22 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -805,25 +805,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -837,13 +837,13 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -863,13 +863,13 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -921,13 +921,13 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:8">
